--- a/data/trans_camb/P19C06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,89</t>
+          <t>-1,31; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,19</t>
+          <t>-1,81; 1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,84</t>
+          <t>-1,14; 5,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,06</t>
+          <t>-1,43; 1,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,5</t>
+          <t>-1,35; 1,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,39</t>
+          <t>-1,46; 1,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,0</t>
+          <t>-0,96; 1,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,06</t>
+          <t>-0,98; 1,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,58</t>
+          <t>-0,97; 2,59</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,95; 731,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 484,53</t>
+          <t>-90,84; 479,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,78; 224,98</t>
+          <t>-67,44; 242,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 243,54</t>
+          <t>-69,08; 245,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,52; 660,14</t>
+          <t>-83,13; 631,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,43</t>
+          <t>-0,75; 1,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,94</t>
+          <t>-0,66; 1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,81</t>
+          <t>-0,93; 1,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,33</t>
+          <t>-0,86; 1,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,97</t>
+          <t>-0,51; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,65</t>
+          <t>-0,81; 1,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,02</t>
+          <t>-0,56; 1,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,47</t>
+          <t>-0,27; 1,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,06</t>
+          <t>-0,59; 1,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-77,13; 811,17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 567,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 947,23</t>
+          <t>-60,61; 629,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,28; 746,22</t>
+          <t>-83,32; 487,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,94; 237,86</t>
+          <t>-62,16; 272,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 343,63</t>
+          <t>-33,27; 357,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 274,14</t>
+          <t>-64,68; 286,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,7</t>
+          <t>-0,75; 1,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,16</t>
+          <t>-1,04; 1,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,1</t>
+          <t>-1,7; 0,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,6</t>
+          <t>-0,46; 2,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,74</t>
+          <t>-1,7; 0,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,37</t>
+          <t>-1,84; 0,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,67</t>
+          <t>-0,23; 1,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,62</t>
+          <t>-1,13; 0,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,04</t>
+          <t>-1,45; -0,0</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,92; 573,64</t>
+          <t>-65,65; 577,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-84,14; 536,38</t>
+          <t>-86,28; 446,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 365,93</t>
+          <t>-33,78; 335,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,51; 135,06</t>
+          <t>-83,11; 110,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,32; 56,34</t>
+          <t>-87,87; 64,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 234,45</t>
+          <t>-18,33; 261,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 86,36</t>
+          <t>-70,69; 107,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-86,39; 18,28</t>
+          <t>-86,82; 10,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,44</t>
+          <t>-0,3; 2,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,56</t>
+          <t>-0,3; 2,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,32</t>
+          <t>-0,7; 1,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,5</t>
+          <t>-2,2; 1,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,34</t>
+          <t>-2,7; 0,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,05</t>
+          <t>-2,25; 0,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,26</t>
+          <t>-0,95; 1,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,8</t>
+          <t>-1,25; 0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,75</t>
+          <t>-1,31; 0,85</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-92,21; —</t>
+          <t>-80,2; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,39; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,8; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 166,17</t>
+          <t>-71,87; 119,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,28; 43,3</t>
+          <t>-87,94; 46,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 90,52</t>
+          <t>-66,74; 81,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,86; 138,68</t>
+          <t>-52,23; 173,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 90,48</t>
+          <t>-64,54; 116,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,35; 93,29</t>
+          <t>-61,46; 99,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,14</t>
+          <t>-4,15; 0,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,55</t>
+          <t>-3,2; 1,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,38</t>
+          <t>-3,55; 0,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,15</t>
+          <t>-1,3; 2,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,27</t>
+          <t>-0,48; 3,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,69</t>
+          <t>-1,22; 1,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,76</t>
+          <t>-1,96; 0,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,04</t>
+          <t>-0,98; 1,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,76</t>
+          <t>-1,68; 0,66</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,22</t>
+          <t>-100,0; 56,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-84,71; 161,43</t>
+          <t>-81,72; 169,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,1; 54,06</t>
+          <t>-86,4; 60,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,27 +1667,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,64; —</t>
+          <t>-59,76; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,24; —</t>
+          <t>-66,76; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-77,82; 99,55</t>
+          <t>-80,56; 102,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 240,53</t>
+          <t>-45,55; 256,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,02; 110,07</t>
+          <t>-66,61; 77,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,68</t>
+          <t>-3,07; 0,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,59</t>
+          <t>-2,38; 2,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,75</t>
+          <t>-3,07; 0,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,54</t>
+          <t>-1,35; 1,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,3</t>
+          <t>-0,99; 2,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,91</t>
+          <t>-1,74; 1,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,82</t>
+          <t>-1,59; 0,77</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,7</t>
+          <t>-1,1; 1,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,48</t>
+          <t>-1,8; 0,61</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>-82,38; 538,09</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-92,05; 181,85</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-92,4; —</t>
+          <t>-86,51; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-82,16; 185,06</t>
+          <t>-85,39; 212,92</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-66,51; 330,36</t>
+          <t>-70,51; 407,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-81,88; 88,92</t>
+          <t>-79,13; 117,6</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -0,74</t>
+          <t>-7,09; -0,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,22</t>
+          <t>-5,49; 1,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,32; -0,12</t>
+          <t>-7,17; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,24</t>
+          <t>-1,28; 2,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,46</t>
+          <t>-0,55; 4,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,04</t>
+          <t>-2,22; 1,04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,63</t>
+          <t>-2,56; 0,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,35</t>
+          <t>-1,66; 2,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,34</t>
+          <t>-2,68; 0,36</t>
         </is>
       </c>
     </row>
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 203,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 567,12</t>
+          <t>-77,86; 467,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-90,41; 104,05</t>
+          <t>-88,33; 138,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,44</t>
+          <t>-0,66; 0,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,72</t>
+          <t>-0,53; 0,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,3</t>
+          <t>-0,84; 0,3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,91</t>
+          <t>-0,27; 0,91</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,74</t>
+          <t>-0,37; 0,78</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,38</t>
+          <t>-0,6; 0,44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,45</t>
+          <t>-0,31; 0,51</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,55</t>
+          <t>-0,27; 0,58</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,27</t>
+          <t>-0,54; 0,21</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 54,42</t>
+          <t>-47,05; 65,45</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 92,43</t>
+          <t>-39,19; 82,75</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 42,57</t>
+          <t>-58,94; 44,67</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 108,3</t>
+          <t>-20,29; 107,56</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 86,53</t>
+          <t>-26,25; 91,49</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 43,48</t>
+          <t>-41,72; 53,12</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 48,82</t>
+          <t>-23,62; 54,46</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 59,02</t>
+          <t>-20,43; 64,77</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 31,47</t>
+          <t>-42,23; 22,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C06-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-0,14</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,85</t>
+          <t>-1,3; 1,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,15</t>
+          <t>-1,83; 1,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,15</t>
+          <t>-1,45; 2,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,08</t>
+          <t>-1,45; 1,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,5</t>
+          <t>-1,08; 1,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,5</t>
+          <t>-1,65; 1,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,05</t>
+          <t>-0,96; 1,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,04</t>
+          <t>-1,01; 1,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,59</t>
+          <t>-1,22; 1,27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-43,88%</t>
+          <t>-43,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>-14,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-88,1; 630,75</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-90,84; 479,98</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,44; 242,33</t>
+          <t>-67,53; 211,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,08; 245,14</t>
+          <t>-71,56; 227,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 631,6</t>
+          <t>-100,0; 314,45</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,31</t>
+          <t>-0,85; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,8</t>
+          <t>-0,6; 1,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,54</t>
+          <t>-1,01; 1,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,42</t>
+          <t>-0,87; 1,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,94</t>
+          <t>-0,41; 1,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,56</t>
+          <t>-0,8; 1,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,0</t>
+          <t>-0,63; 0,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,42</t>
+          <t>-0,29; 1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,05</t>
+          <t>-0,71; 0,98</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>-14,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 811,17</t>
+          <t>-75,97; 647,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-73,59; 780,8</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 567,38</t>
+          <t>-94,58; 561,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,61; 629,46</t>
+          <t>-52,52; 660,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,32; 487,48</t>
+          <t>-78,63; 603,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 272,93</t>
+          <t>-59,43; 263,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 357,48</t>
+          <t>-39,17; 368,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,68; 286,14</t>
+          <t>-67,65; 229,35</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,58</t>
+          <t>-0,66; 1,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,07</t>
+          <t>-1,16; 1,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,04</t>
+          <t>-1,73; 0,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,63</t>
+          <t>-0,36; 2,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,73</t>
+          <t>-1,75; 0,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,31</t>
+          <t>-1,89; 0,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,7</t>
+          <t>-0,24; 1,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,57</t>
+          <t>-1,12; 0,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; -0,0</t>
+          <t>-1,36; 0,1</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-75,08%</t>
+          <t>-75,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-48,05%</t>
+          <t>-43,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-58,68%</t>
+          <t>-56,18%</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,65; 577,97</t>
+          <t>-68,67; 593,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-86,28; 446,28</t>
+          <t>-100,0; 358,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 335,66</t>
+          <t>-25,51; 353,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,11; 110,87</t>
+          <t>-81,01; 154,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,87; 64,47</t>
+          <t>-85,15; 92,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 261,37</t>
+          <t>-20,56; 231,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,69; 107,72</t>
+          <t>-72,17; 91,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-86,82; 10,97</t>
+          <t>-83,58; 27,6</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,36</t>
+          <t>-0,35; 2,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,48</t>
+          <t>-0,29; 2,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,42</t>
+          <t>-0,38; 1,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,38</t>
+          <t>-2,09; 1,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,45</t>
+          <t>-2,92; 0,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,94</t>
+          <t>-2,17; 0,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,39</t>
+          <t>-0,9; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,84</t>
+          <t>-1,28; 0,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,85</t>
+          <t>-1,0; 0,9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>134,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-20,59%</t>
+          <t>-27,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-9,42%</t>
+          <t>-0,41%</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-80,2; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,87; 119,91</t>
+          <t>-65,32; 140,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,94; 46,97</t>
+          <t>-88,46; 69,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 81,93</t>
+          <t>-67,32; 71,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 173,45</t>
+          <t>-48,21; 164,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 116,89</t>
+          <t>-66,38; 107,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,46; 99,69</t>
+          <t>-53,82; 115,76</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,11</t>
+          <t>-3,91; 0,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,48</t>
+          <t>-3,13; 1,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,34</t>
+          <t>-3,91; 0,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,13</t>
+          <t>-1,32; 1,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,42</t>
+          <t>-0,62; 3,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,63</t>
+          <t>-1,46; 1,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,74</t>
+          <t>-1,93; 0,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,92</t>
+          <t>-1,06; 2,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,66</t>
+          <t>-1,82; 0,55</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-54,52%</t>
+          <t>-58,29%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-17,99%</t>
+          <t>-21,02%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,61</t>
+          <t>-100,0; 53,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-81,72; 169,17</t>
+          <t>-85,13; 166,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,4; 60,27</t>
+          <t>-88,64; 28,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,27 +1667,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-59,76; —</t>
+          <t>-70,42; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,76; —</t>
+          <t>-68,24; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-80,56; 102,57</t>
+          <t>-78,87; 102,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,55; 256,62</t>
+          <t>-47,76; 214,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 77,78</t>
+          <t>-65,26; 69,11</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,78</t>
+          <t>-3,22; 0,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,58</t>
+          <t>-2,13; 2,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,71</t>
+          <t>-2,88; 0,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,55</t>
+          <t>-1,4; 1,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,31</t>
+          <t>-0,81; 2,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,0</t>
+          <t>-1,29; 1,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,77</t>
+          <t>-1,56; 0,8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,79</t>
+          <t>-0,95; 1,69</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,61</t>
+          <t>-1,42; 0,76</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-41,65%</t>
+          <t>-46,2%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-29,48%</t>
+          <t>-14,04%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 538,09</t>
+          <t>-88,56; 567,36</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-92,05; 181,85</t>
+          <t>-88,45; 193,11</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-86,51; —</t>
+          <t>-86,06; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-85,39; 212,92</t>
+          <t>-84,66; 202,78</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-70,51; 407,95</t>
+          <t>-64,66; 335,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-79,13; 117,6</t>
+          <t>-70,96; 179,55</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -0,72</t>
+          <t>-7,5; -0,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1,56</t>
+          <t>-6,02; 1,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 0,0</t>
+          <t>-7,27; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,23</t>
+          <t>-1,04; 2,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,24</t>
+          <t>-0,54; 4,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,04</t>
+          <t>-1,61; 0,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,61</t>
+          <t>-2,63; 0,6</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,27</t>
+          <t>-1,6; 2,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,36</t>
+          <t>-2,99; 0,22</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-84,21%</t>
+          <t>-85,6%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-53,58%</t>
+          <t>-55,83%</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-77,86; 467,48</t>
+          <t>-79,61; 464,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-88,33; 138,97</t>
+          <t>-89,26; 51,24</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,47</t>
+          <t>-0,69; 0,45</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,68</t>
+          <t>-0,52; 0,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,3</t>
+          <t>-0,85; 0,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,91</t>
+          <t>-0,29; 0,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,78</t>
+          <t>-0,37; 0,83</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,44</t>
+          <t>-0,55; 0,44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,51</t>
+          <t>-0,32; 0,5</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,58</t>
+          <t>-0,27; 0,57</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,21</t>
+          <t>-0,54; 0,18</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-24,4%</t>
+          <t>-29,98%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-6,64%</t>
+          <t>-3,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>-15,94%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 65,45</t>
+          <t>-49,15; 57,79</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 82,75</t>
+          <t>-39,22; 80,74</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-58,94; 44,67</t>
+          <t>-61,84; 27,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 107,56</t>
+          <t>-22,06; 101,26</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 91,49</t>
+          <t>-26,75; 100,42</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-41,72; 53,12</t>
+          <t>-38,07; 54,35</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 54,46</t>
+          <t>-25,54; 55,42</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 64,77</t>
+          <t>-20,3; 63,09</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 22,38</t>
+          <t>-39,84; 20,75</t>
         </is>
       </c>
     </row>
